--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419433</v>
+        <v>123419431</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>90957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -727,7 +727,7 @@
         <v>602006</v>
       </c>
       <c r="R2" t="n">
-        <v>6887727</v>
+        <v>6887720</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2201</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419431</v>
+        <v>123419433</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,7 +857,7 @@
         <v>602006</v>
       </c>
       <c r="R3" t="n">
-        <v>6887720</v>
+        <v>6887727</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2201</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419444</v>
+        <v>123419446</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602135</v>
+        <v>602188</v>
       </c>
       <c r="R4" t="n">
-        <v>6887783</v>
+        <v>6887831</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2194</t>
+          <t>2024_2193</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419436</v>
+        <v>123419444</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>79852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1110,14 +1110,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lommen SO om, Hls</t>
+          <t>Lommen, no om, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601998</v>
+        <v>602135</v>
       </c>
       <c r="R5" t="n">
-        <v>6887724</v>
+        <v>6887783</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2198</t>
+          <t>2024_2194</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1198,7 +1198,7 @@
         <v>123419435</v>
       </c>
       <c r="B6" t="n">
-        <v>91304</v>
+        <v>91306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419446</v>
+        <v>123419436</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>90957</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1375,14 +1375,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lommen, no om, Hls</t>
+          <t>Lommen SO om, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602188</v>
+        <v>601998</v>
       </c>
       <c r="R7" t="n">
-        <v>6887831</v>
+        <v>6887724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2193</t>
+          <t>2024_2198</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419431</v>
+        <v>123419435</v>
       </c>
       <c r="B2" t="n">
-        <v>90957</v>
+        <v>91312</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602006</v>
+        <v>601998</v>
       </c>
       <c r="R2" t="n">
-        <v>6887720</v>
+        <v>6887731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2201</t>
+          <t>2024_2199</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På utgången ullticka, grövre granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419433</v>
+        <v>123419446</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602006</v>
+        <v>602188</v>
       </c>
       <c r="R3" t="n">
-        <v>6887727</v>
+        <v>6887831</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2193</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419446</v>
+        <v>123419433</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602188</v>
+        <v>602006</v>
       </c>
       <c r="R4" t="n">
-        <v>6887831</v>
+        <v>6887727</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2193</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419444</v>
+        <v>123419431</v>
       </c>
       <c r="B5" t="n">
-        <v>79852</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,7 +1110,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602135</v>
+        <v>602006</v>
       </c>
       <c r="R5" t="n">
-        <v>6887783</v>
+        <v>6887720</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2194</t>
+          <t>2024_2201</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1169,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419435</v>
+        <v>123419444</v>
       </c>
       <c r="B6" t="n">
-        <v>91306</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,25 +1212,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,7 +1240,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601998</v>
+        <v>602135</v>
       </c>
       <c r="R6" t="n">
-        <v>6887731</v>
+        <v>6887783</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2199</t>
+          <t>2024_2194</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1289,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1299,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På utgången ullticka, grövre granlåga</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1333,7 +1333,7 @@
         <v>123419436</v>
       </c>
       <c r="B7" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419435</v>
+        <v>123419436</v>
       </c>
       <c r="B2" t="n">
-        <v>91312</v>
+        <v>90966</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lommen, no om, Hls</t>
+          <t>Lommen SO om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>601998</v>
       </c>
       <c r="R2" t="n">
-        <v>6887731</v>
+        <v>6887724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2199</t>
+          <t>2024_2198</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På utgången ullticka, grövre granlåga</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419446</v>
+        <v>123419431</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>90966</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,7 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602188</v>
+        <v>602006</v>
       </c>
       <c r="R3" t="n">
-        <v>6887831</v>
+        <v>6887720</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2193</t>
+          <t>2024_2201</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419433</v>
+        <v>123419446</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602006</v>
+        <v>602188</v>
       </c>
       <c r="R4" t="n">
-        <v>6887727</v>
+        <v>6887831</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2193</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419431</v>
+        <v>123419433</v>
       </c>
       <c r="B5" t="n">
-        <v>90963</v>
+        <v>78775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1081,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1110,7 +1105,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1122,7 +1117,7 @@
         <v>602006</v>
       </c>
       <c r="R5" t="n">
-        <v>6887720</v>
+        <v>6887727</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2201</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419444</v>
+        <v>123419435</v>
       </c>
       <c r="B6" t="n">
-        <v>79853</v>
+        <v>91315</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,25 +1207,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1240,7 +1235,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1249,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602135</v>
+        <v>601998</v>
       </c>
       <c r="R6" t="n">
-        <v>6887783</v>
+        <v>6887731</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2194</t>
+          <t>2024_2199</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1289,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1299,7 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På utgången ullticka, grövre granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419436</v>
+        <v>123419444</v>
       </c>
       <c r="B7" t="n">
-        <v>90963</v>
+        <v>79856</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1375,14 +1375,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lommen SO om, Hls</t>
+          <t>Lommen, no om, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601998</v>
+        <v>602135</v>
       </c>
       <c r="R7" t="n">
-        <v>6887724</v>
+        <v>6887783</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2198</t>
+          <t>2024_2194</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419436</v>
+        <v>123419446</v>
       </c>
       <c r="B2" t="n">
-        <v>90966</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lommen SO om, Hls</t>
+          <t>Lommen, no om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601998</v>
+        <v>602188</v>
       </c>
       <c r="R2" t="n">
-        <v>6887724</v>
+        <v>6887831</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2198</t>
+          <t>2024_2193</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419431</v>
+        <v>123419436</v>
       </c>
       <c r="B3" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lommen, no om, Hls</t>
+          <t>Lommen SO om, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602006</v>
+        <v>601998</v>
       </c>
       <c r="R3" t="n">
-        <v>6887720</v>
+        <v>6887724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2201</t>
+          <t>2024_2198</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419446</v>
+        <v>123419444</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602188</v>
+        <v>602135</v>
       </c>
       <c r="R4" t="n">
-        <v>6887831</v>
+        <v>6887783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2193</t>
+          <t>2024_2194</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419433</v>
+        <v>123419431</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1117,7 +1117,7 @@
         <v>602006</v>
       </c>
       <c r="R5" t="n">
-        <v>6887727</v>
+        <v>6887720</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2201</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,7 +1198,7 @@
         <v>123419435</v>
       </c>
       <c r="B6" t="n">
-        <v>91315</v>
+        <v>91332</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419444</v>
+        <v>123419433</v>
       </c>
       <c r="B7" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602135</v>
+        <v>602006</v>
       </c>
       <c r="R7" t="n">
-        <v>6887783</v>
+        <v>6887727</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2194</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419435</v>
+        <v>123419433</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601998</v>
+        <v>602006</v>
       </c>
       <c r="R6" t="n">
-        <v>6887731</v>
+        <v>6887727</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2199</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På utgången ullticka, grövre granlåga</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419433</v>
+        <v>123419435</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>91332</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1337,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1370,7 +1365,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602006</v>
+        <v>601998</v>
       </c>
       <c r="R7" t="n">
-        <v>6887727</v>
+        <v>6887731</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2199</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1424,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På utgången ullticka, grövre granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419433</v>
+        <v>123419435</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>91332</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602006</v>
+        <v>601998</v>
       </c>
       <c r="R6" t="n">
-        <v>6887727</v>
+        <v>6887731</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2199</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På utgången ullticka, grövre granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419435</v>
+        <v>123419433</v>
       </c>
       <c r="B7" t="n">
-        <v>91332</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1365,7 +1370,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601998</v>
+        <v>602006</v>
       </c>
       <c r="R7" t="n">
-        <v>6887731</v>
+        <v>6887727</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2199</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,12 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På utgången ullticka, grövre granlåga</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419446</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419436</v>
+        <v>123419431</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lommen SO om, Hls</t>
+          <t>Lommen, no om, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601998</v>
+        <v>602006</v>
       </c>
       <c r="R3" t="n">
-        <v>6887724</v>
+        <v>6887720</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2198</t>
+          <t>2024_2201</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419444</v>
+        <v>123419435</v>
       </c>
       <c r="B4" t="n">
-        <v>79862</v>
+        <v>91337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602135</v>
+        <v>601998</v>
       </c>
       <c r="R4" t="n">
-        <v>6887783</v>
+        <v>6887731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2194</t>
+          <t>2024_2199</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På utgången ullticka, grövre granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419431</v>
+        <v>123419433</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,7 +1110,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1117,7 +1122,7 @@
         <v>602006</v>
       </c>
       <c r="R5" t="n">
-        <v>6887720</v>
+        <v>6887727</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2201</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1169,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419435</v>
+        <v>123419444</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>79867</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,25 +1212,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,7 +1240,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601998</v>
+        <v>602135</v>
       </c>
       <c r="R6" t="n">
-        <v>6887731</v>
+        <v>6887783</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2199</t>
+          <t>2024_2194</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1289,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1299,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På utgången ullticka, grövre granlåga</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419433</v>
+        <v>123419436</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>90988</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1375,14 +1375,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lommen, no om, Hls</t>
+          <t>Lommen SO om, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602006</v>
+        <v>601998</v>
       </c>
       <c r="R7" t="n">
-        <v>6887727</v>
+        <v>6887724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2198</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419446</v>
+        <v>123419433</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602188</v>
+        <v>602006</v>
       </c>
       <c r="R2" t="n">
-        <v>6887831</v>
+        <v>6887727</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2193</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,7 +808,7 @@
         <v>123419431</v>
       </c>
       <c r="B3" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419435</v>
+        <v>123419436</v>
       </c>
       <c r="B4" t="n">
-        <v>91337</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,19 +975,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lommen, no om, Hls</t>
+          <t>Lommen SO om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>601998</v>
       </c>
       <c r="R4" t="n">
-        <v>6887731</v>
+        <v>6887724</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2199</t>
+          <t>2024_2198</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På utgången ullticka, grövre granlåga</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1070,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419433</v>
+        <v>123419446</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602006</v>
+        <v>602188</v>
       </c>
       <c r="R5" t="n">
-        <v>6887727</v>
+        <v>6887831</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2193</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1203,7 +1198,7 @@
         <v>123419444</v>
       </c>
       <c r="B6" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1330,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419436</v>
+        <v>123419435</v>
       </c>
       <c r="B7" t="n">
-        <v>90988</v>
+        <v>91339</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1337,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1370,19 +1365,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lommen SO om, Hls</t>
+          <t>Lommen, no om, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>601998</v>
       </c>
       <c r="R7" t="n">
-        <v>6887724</v>
+        <v>6887731</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2198</t>
+          <t>2024_2199</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1424,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På utgången ullticka, grövre granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419431</v>
+        <v>123419435</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>91339</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602006</v>
+        <v>601998</v>
       </c>
       <c r="R3" t="n">
-        <v>6887720</v>
+        <v>6887731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2201</t>
+          <t>2024_2199</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På utgången ullticka, grövre granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,7 +940,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419436</v>
+        <v>123419431</v>
       </c>
       <c r="B4" t="n">
         <v>90990</v>
@@ -975,19 +980,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lommen SO om, Hls</t>
+          <t>Lommen, no om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601998</v>
+        <v>602006</v>
       </c>
       <c r="R4" t="n">
-        <v>6887724</v>
+        <v>6887720</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2198</t>
+          <t>2024_2201</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419446</v>
+        <v>123419436</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1110,14 +1115,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lommen, no om, Hls</t>
+          <t>Lommen SO om, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602188</v>
+        <v>601998</v>
       </c>
       <c r="R5" t="n">
-        <v>6887831</v>
+        <v>6887724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2193</t>
+          <t>2024_2198</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1169,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1189,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1325,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419435</v>
+        <v>123419446</v>
       </c>
       <c r="B7" t="n">
-        <v>91339</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1365,7 +1370,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601998</v>
+        <v>602188</v>
       </c>
       <c r="R7" t="n">
-        <v>6887731</v>
+        <v>6887831</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2199</t>
+          <t>2024_2193</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,12 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På utgången ullticka, grövre granlåga</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419433</v>
+        <v>123419444</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602006</v>
+        <v>602135</v>
       </c>
       <c r="R2" t="n">
-        <v>6887727</v>
+        <v>6887783</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2194</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419435</v>
+        <v>123419431</v>
       </c>
       <c r="B3" t="n">
-        <v>91339</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601998</v>
+        <v>602006</v>
       </c>
       <c r="R3" t="n">
-        <v>6887731</v>
+        <v>6887720</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2199</t>
+          <t>2024_2201</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På utgången ullticka, grövre granlåga</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419431</v>
+        <v>123419435</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>91339</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -989,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602006</v>
+        <v>601998</v>
       </c>
       <c r="R4" t="n">
-        <v>6887720</v>
+        <v>6887731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2201</t>
+          <t>2024_2199</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1034,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På utgången ullticka, grövre granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419436</v>
+        <v>123419433</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1115,14 +1115,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lommen SO om, Hls</t>
+          <t>Lommen, no om, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601998</v>
+        <v>602006</v>
       </c>
       <c r="R5" t="n">
-        <v>6887724</v>
+        <v>6887727</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2198</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419444</v>
+        <v>123419446</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602135</v>
+        <v>602188</v>
       </c>
       <c r="R6" t="n">
-        <v>6887783</v>
+        <v>6887831</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2194</t>
+          <t>2024_2193</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419446</v>
+        <v>123419436</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1375,14 +1375,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lommen, no om, Hls</t>
+          <t>Lommen SO om, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602188</v>
+        <v>601998</v>
       </c>
       <c r="R7" t="n">
-        <v>6887831</v>
+        <v>6887724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2193</t>
+          <t>2024_2198</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419444</v>
+        <v>123419436</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lommen, no om, Hls</t>
+          <t>Lommen SO om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602135</v>
+        <v>601998</v>
       </c>
       <c r="R2" t="n">
-        <v>6887783</v>
+        <v>6887724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2194</t>
+          <t>2024_2198</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419435</v>
+        <v>123419446</v>
       </c>
       <c r="B4" t="n">
-        <v>91339</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601998</v>
+        <v>602188</v>
       </c>
       <c r="R4" t="n">
-        <v>6887731</v>
+        <v>6887831</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2199</t>
+          <t>2024_2193</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På utgången ullticka, grövre granlåga</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419433</v>
+        <v>123419444</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1081,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1119,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602006</v>
+        <v>602135</v>
       </c>
       <c r="R5" t="n">
-        <v>6887727</v>
+        <v>6887783</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2194</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419446</v>
+        <v>123419435</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>91339</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,25 +1207,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1240,7 +1235,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1249,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602188</v>
+        <v>601998</v>
       </c>
       <c r="R6" t="n">
-        <v>6887831</v>
+        <v>6887731</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2193</t>
+          <t>2024_2199</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1289,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1299,7 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På utgången ullticka, grövre granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419436</v>
+        <v>123419433</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1375,14 +1375,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lommen SO om, Hls</t>
+          <t>Lommen, no om, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601998</v>
+        <v>602006</v>
       </c>
       <c r="R7" t="n">
-        <v>6887724</v>
+        <v>6887727</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2198</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419436</v>
+        <v>123419431</v>
       </c>
       <c r="B2" t="n">
         <v>90990</v>
@@ -715,19 +715,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lommen SO om, Hls</t>
+          <t>Lommen, no om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601998</v>
+        <v>602006</v>
       </c>
       <c r="R2" t="n">
-        <v>6887724</v>
+        <v>6887720</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2198</t>
+          <t>2024_2201</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419431</v>
+        <v>123419435</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>91339</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602006</v>
+        <v>601998</v>
       </c>
       <c r="R3" t="n">
-        <v>6887720</v>
+        <v>6887731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2201</t>
+          <t>2024_2199</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På utgången ullticka, grövre granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,7 +940,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419446</v>
+        <v>123419433</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -984,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602188</v>
+        <v>602006</v>
       </c>
       <c r="R4" t="n">
-        <v>6887831</v>
+        <v>6887727</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2193</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419444</v>
+        <v>123419446</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1114,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602135</v>
+        <v>602188</v>
       </c>
       <c r="R5" t="n">
-        <v>6887783</v>
+        <v>6887831</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2194</t>
+          <t>2024_2193</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1169,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419435</v>
+        <v>123419444</v>
       </c>
       <c r="B6" t="n">
-        <v>91339</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,25 +1212,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,7 +1240,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601998</v>
+        <v>602135</v>
       </c>
       <c r="R6" t="n">
-        <v>6887731</v>
+        <v>6887783</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2199</t>
+          <t>2024_2194</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1289,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1299,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På utgången ullticka, grövre granlåga</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419433</v>
+        <v>123419436</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1375,14 +1375,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lommen, no om, Hls</t>
+          <t>Lommen SO om, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602006</v>
+        <v>601998</v>
       </c>
       <c r="R7" t="n">
-        <v>6887727</v>
+        <v>6887724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2198</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 14052-2025 artfynd.xlsx
+++ b/artfynd/A 14052-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419431</v>
+        <v>123419444</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602006</v>
+        <v>602135</v>
       </c>
       <c r="R2" t="n">
-        <v>6887720</v>
+        <v>6887783</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2201</t>
+          <t>2024_2194</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419433</v>
+        <v>123419436</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,21 +956,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -985,14 +985,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lommen, no om, Hls</t>
+          <t>Lommen SO om, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602006</v>
+        <v>601998</v>
       </c>
       <c r="R4" t="n">
-        <v>6887727</v>
+        <v>6887724</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2200</t>
+          <t>2024_2198</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419444</v>
+        <v>123419431</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602135</v>
+        <v>602006</v>
       </c>
       <c r="R6" t="n">
-        <v>6887783</v>
+        <v>6887720</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2194</t>
+          <t>2024_2201</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419436</v>
+        <v>123419433</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1375,14 +1375,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lommen SO om, Hls</t>
+          <t>Lommen, no om, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601998</v>
+        <v>602006</v>
       </c>
       <c r="R7" t="n">
-        <v>6887724</v>
+        <v>6887727</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2198</t>
+          <t>2024_2200</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
